--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/137.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/137.xlsx
@@ -426,13 +426,13 @@
         <v>-15.52849165671437</v>
       </c>
       <c r="E2">
-        <v>-15.56033237072979</v>
+        <v>-15.48476119648978</v>
       </c>
       <c r="F2">
-        <v>4.713780654910731</v>
+        <v>5.033318410336223</v>
       </c>
       <c r="G2">
-        <v>-12.47521929103351</v>
+        <v>-13.38313971572417</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.40729644456917</v>
       </c>
       <c r="E3">
-        <v>-15.50850851418601</v>
+        <v>-17.20164154701785</v>
       </c>
       <c r="F3">
-        <v>4.747859689861902</v>
+        <v>4.949288820996241</v>
       </c>
       <c r="G3">
-        <v>-12.21482502109659</v>
+        <v>-12.62361780537688</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.21363266538785</v>
       </c>
       <c r="E4">
-        <v>-16.8813878651954</v>
+        <v>-16.52459845507907</v>
       </c>
       <c r="F4">
-        <v>4.888471743017507</v>
+        <v>5.468658615203475</v>
       </c>
       <c r="G4">
-        <v>-12.71122808252815</v>
+        <v>-11.8392370085752</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.94217517672816</v>
       </c>
       <c r="E5">
-        <v>-17.10616320104013</v>
+        <v>-17.74904348506504</v>
       </c>
       <c r="F5">
-        <v>4.921745604853157</v>
+        <v>5.273498568573523</v>
       </c>
       <c r="G5">
-        <v>-10.54919355446862</v>
+        <v>-11.68747829050947</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.60617815962045</v>
       </c>
       <c r="E6">
-        <v>-18.29977837998188</v>
+        <v>-19.01694828010262</v>
       </c>
       <c r="F6">
-        <v>4.990947417683028</v>
+        <v>5.117286700488398</v>
       </c>
       <c r="G6">
-        <v>-10.11385019496338</v>
+        <v>-11.77145027811308</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.20384754216078</v>
       </c>
       <c r="E7">
-        <v>-18.87119481569174</v>
+        <v>-19.64666429018724</v>
       </c>
       <c r="F7">
-        <v>5.210140059403</v>
+        <v>5.605354147278644</v>
       </c>
       <c r="G7">
-        <v>-10.33428618024129</v>
+        <v>-10.25958372014764</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.74515780742966</v>
       </c>
       <c r="E8">
-        <v>-19.81646395157885</v>
+        <v>-20.20218578213019</v>
       </c>
       <c r="F8">
-        <v>5.128100208564542</v>
+        <v>5.436388734660017</v>
       </c>
       <c r="G8">
-        <v>-8.823061868110466</v>
+        <v>-9.913280793466637</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.21986799824624</v>
       </c>
       <c r="E9">
-        <v>-21.12185998292594</v>
+        <v>-20.86194368878169</v>
       </c>
       <c r="F9">
-        <v>5.178869189947319</v>
+        <v>5.433355253230966</v>
       </c>
       <c r="G9">
-        <v>-8.286491957650933</v>
+        <v>-8.968477580922954</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.63073439284912</v>
       </c>
       <c r="E10">
-        <v>-21.48306465519975</v>
+        <v>-21.78510028608934</v>
       </c>
       <c r="F10">
-        <v>5.465157934559245</v>
+        <v>5.28285083655113</v>
       </c>
       <c r="G10">
-        <v>-7.614037394986473</v>
+        <v>-8.746879594160758</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.96145428371551</v>
       </c>
       <c r="E11">
-        <v>-22.30051308374635</v>
+        <v>-22.92331411402125</v>
       </c>
       <c r="F11">
-        <v>5.557300554242245</v>
+        <v>5.63245998543305</v>
       </c>
       <c r="G11">
-        <v>-6.88667412400766</v>
+        <v>-6.83902544206093</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.21827370008922</v>
       </c>
       <c r="E12">
-        <v>-22.95233710393641</v>
+        <v>-23.6055921219129</v>
       </c>
       <c r="F12">
-        <v>5.509298319984819</v>
+        <v>5.561811843117891</v>
       </c>
       <c r="G12">
-        <v>-6.64611333239652</v>
+        <v>-6.8971222057296</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.39365854344571</v>
       </c>
       <c r="E13">
-        <v>-23.96393479861386</v>
+        <v>-24.13007545300727</v>
       </c>
       <c r="F13">
-        <v>5.642904041647546</v>
+        <v>5.464702332487705</v>
       </c>
       <c r="G13">
-        <v>-4.955185987302976</v>
+        <v>-5.328390407036095</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.508516966626914</v>
       </c>
       <c r="E14">
-        <v>-25.4518509748401</v>
+        <v>-25.9951818147544</v>
       </c>
       <c r="F14">
-        <v>6.220284405072829</v>
+        <v>6.144507011799536</v>
       </c>
       <c r="G14">
-        <v>-4.6965231326831</v>
+        <v>-4.209121444572821</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.5719486756542</v>
       </c>
       <c r="E15">
-        <v>-26.01166546014232</v>
+        <v>-26.59095238367752</v>
       </c>
       <c r="F15">
-        <v>5.980733806061656</v>
+        <v>5.758971568658201</v>
       </c>
       <c r="G15">
-        <v>-3.653025936522665</v>
+        <v>-4.771139518592733</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.613246262250276</v>
       </c>
       <c r="E16">
-        <v>-26.53920551119187</v>
+        <v>-27.01303786051045</v>
       </c>
       <c r="F16">
-        <v>6.297849415201363</v>
+        <v>6.276220742314268</v>
       </c>
       <c r="G16">
-        <v>-3.870177860625619</v>
+        <v>-3.15179609969485</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.652814896670857</v>
       </c>
       <c r="E17">
-        <v>-27.78443170839904</v>
+        <v>-28.23971995665621</v>
       </c>
       <c r="F17">
-        <v>6.163619104516926</v>
+        <v>6.397208771697553</v>
       </c>
       <c r="G17">
-        <v>-3.609339977586442</v>
+        <v>-2.105038016178232</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.721481544853012</v>
       </c>
       <c r="E18">
-        <v>-29.22063271145769</v>
+        <v>-28.75964311442486</v>
       </c>
       <c r="F18">
-        <v>6.613727443441288</v>
+        <v>6.488673786845063</v>
       </c>
       <c r="G18">
-        <v>-2.380246977403385</v>
+        <v>-2.431312142346644</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.844964722166633</v>
       </c>
       <c r="E19">
-        <v>-29.15029645317055</v>
+        <v>-29.44044936826402</v>
       </c>
       <c r="F19">
-        <v>6.460269068603068</v>
+        <v>6.800376843374878</v>
       </c>
       <c r="G19">
-        <v>-1.968017846853337</v>
+        <v>-1.453168425676961</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.050802249730575</v>
       </c>
       <c r="E20">
-        <v>-30.13552937217534</v>
+        <v>-29.89125442725359</v>
       </c>
       <c r="F20">
-        <v>6.652924132206955</v>
+        <v>6.738845712694931</v>
       </c>
       <c r="G20">
-        <v>-1.479089997249454</v>
+        <v>-0.7113380706915339</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.363335818622474</v>
       </c>
       <c r="E21">
-        <v>-30.67624048987621</v>
+        <v>-30.19953935227377</v>
       </c>
       <c r="F21">
-        <v>6.715974488703637</v>
+        <v>7.016338852223932</v>
       </c>
       <c r="G21">
-        <v>-1.410343208580949</v>
+        <v>-1.393340246691252</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.798823228784502</v>
       </c>
       <c r="E22">
-        <v>-31.00294045444857</v>
+        <v>-31.09669345182937</v>
       </c>
       <c r="F22">
-        <v>6.621843787253917</v>
+        <v>7.140651948362053</v>
       </c>
       <c r="G22">
-        <v>-1.182044677647268</v>
+        <v>-0.2337918766516651</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.369976290836088</v>
       </c>
       <c r="E23">
-        <v>-31.05540735430144</v>
+        <v>-31.03646021905335</v>
       </c>
       <c r="F23">
-        <v>6.71703479897922</v>
+        <v>7.002491862718735</v>
       </c>
       <c r="G23">
-        <v>-0.3445395565769042</v>
+        <v>-0.4028316424323912</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.075594517985133</v>
       </c>
       <c r="E24">
-        <v>-31.63045789040246</v>
+        <v>-31.02856708885798</v>
       </c>
       <c r="F24">
-        <v>6.867946772421234</v>
+        <v>6.837394925871182</v>
       </c>
       <c r="G24">
-        <v>-1.130919922884303</v>
+        <v>0.405742621170282</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.912875938274533</v>
       </c>
       <c r="E25">
-        <v>-31.29094234438839</v>
+        <v>-32.06350001009695</v>
       </c>
       <c r="F25">
-        <v>6.616755954665923</v>
+        <v>7.045450996227918</v>
       </c>
       <c r="G25">
-        <v>-0.357295088539716</v>
+        <v>0.8410462541290504</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.86468947206207</v>
       </c>
       <c r="E26">
-        <v>-32.00021005736576</v>
+        <v>-31.36088462543686</v>
       </c>
       <c r="F26">
-        <v>6.380298479536804</v>
+        <v>7.004493198363899</v>
       </c>
       <c r="G26">
-        <v>-0.7721693449756419</v>
+        <v>0.8541990515565748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.915255718851313</v>
       </c>
       <c r="E27">
-        <v>-31.75667098947024</v>
+        <v>-30.16197113190613</v>
       </c>
       <c r="F27">
-        <v>6.637138762979207</v>
+        <v>6.410900028131024</v>
       </c>
       <c r="G27">
-        <v>-0.4188977199344743</v>
+        <v>-0.115962939817925</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.039701682707649</v>
       </c>
       <c r="E28">
-        <v>-30.98143020291214</v>
+        <v>-30.80155242261646</v>
       </c>
       <c r="F28">
-        <v>6.780640161635777</v>
+        <v>6.925705517948832</v>
       </c>
       <c r="G28">
-        <v>-0.7157212329855289</v>
+        <v>-0.2594287413077812</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.21879845000305</v>
       </c>
       <c r="E29">
-        <v>-30.8275526561315</v>
+        <v>-30.74090936294274</v>
       </c>
       <c r="F29">
-        <v>6.468869178978933</v>
+        <v>6.374032708502028</v>
       </c>
       <c r="G29">
-        <v>-0.6643084607606474</v>
+        <v>-0.4485204814198729</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.43076623485136</v>
       </c>
       <c r="E30">
-        <v>-30.6561046302011</v>
+        <v>-29.60942937586023</v>
       </c>
       <c r="F30">
-        <v>6.600534864184303</v>
+        <v>7.044736943526704</v>
       </c>
       <c r="G30">
-        <v>-1.051529730307041</v>
+        <v>-0.5097126051677615</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.659895980101855</v>
       </c>
       <c r="E31">
-        <v>-31.06191024297646</v>
+        <v>-29.90722409084164</v>
       </c>
       <c r="F31">
-        <v>6.740830480992038</v>
+        <v>6.921202512747214</v>
       </c>
       <c r="G31">
-        <v>-0.3456055522405495</v>
+        <v>-0.00456639296698888</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.893170099827508</v>
       </c>
       <c r="E32">
-        <v>-29.66100416633359</v>
+        <v>-29.62550545858747</v>
       </c>
       <c r="F32">
-        <v>6.517689840230324</v>
+        <v>6.717715716984321</v>
       </c>
       <c r="G32">
-        <v>-1.423015976905279</v>
+        <v>-0.6616467821470734</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.120519932396506</v>
       </c>
       <c r="E33">
-        <v>-30.29435201257236</v>
+        <v>-30.13289832877689</v>
       </c>
       <c r="F33">
-        <v>6.891271941749262</v>
+        <v>6.841763735553547</v>
       </c>
       <c r="G33">
-        <v>-1.539818644621845</v>
+        <v>-1.652357329683829</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.337875523115534</v>
       </c>
       <c r="E34">
-        <v>-29.37504008969722</v>
+        <v>-28.22513374187751</v>
       </c>
       <c r="F34">
-        <v>6.807929897353604</v>
+        <v>6.48692096142074</v>
       </c>
       <c r="G34">
-        <v>-1.720829343072575</v>
+        <v>-1.760357256811473</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.539912506900463</v>
       </c>
       <c r="E35">
-        <v>-29.21589139917166</v>
+        <v>-28.08513143945637</v>
       </c>
       <c r="F35">
-        <v>6.847027182030935</v>
+        <v>6.738270825717388</v>
       </c>
       <c r="G35">
-        <v>-2.647166332598204</v>
+        <v>-1.730429925136462</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.728834670648419</v>
       </c>
       <c r="E36">
-        <v>-28.21386689854642</v>
+        <v>-28.37419299231398</v>
       </c>
       <c r="F36">
-        <v>7.156072835932569</v>
+        <v>7.154878330137732</v>
       </c>
       <c r="G36">
-        <v>-2.040310229794402</v>
+        <v>-2.322166766462411</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.903744008269409</v>
       </c>
       <c r="E37">
-        <v>-28.36249141547816</v>
+        <v>-27.82152443899587</v>
       </c>
       <c r="F37">
-        <v>7.159262050433347</v>
+        <v>6.767523792179849</v>
       </c>
       <c r="G37">
-        <v>-2.763161227203187</v>
+        <v>-3.462878132383545</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.071878579568477</v>
       </c>
       <c r="E38">
-        <v>-27.17090952136585</v>
+        <v>-26.44302525174296</v>
       </c>
       <c r="F38">
-        <v>7.028048653829905</v>
+        <v>7.104937716157756</v>
       </c>
       <c r="G38">
-        <v>-2.870972453235093</v>
+        <v>-2.801828399101875</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.23586643302502</v>
       </c>
       <c r="E39">
-        <v>-27.11952492680082</v>
+        <v>-25.68742219271912</v>
       </c>
       <c r="F39">
-        <v>7.061920596930377</v>
+        <v>7.659453482530967</v>
       </c>
       <c r="G39">
-        <v>-3.289240018848772</v>
+        <v>-3.3755062145111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.403512059014047</v>
       </c>
       <c r="E40">
-        <v>-25.96719131691299</v>
+        <v>-25.39671227532271</v>
       </c>
       <c r="F40">
-        <v>7.407369684715438</v>
+        <v>7.302167024559901</v>
       </c>
       <c r="G40">
-        <v>-4.117740456052318</v>
+        <v>-3.027293103053939</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.575321774461404</v>
       </c>
       <c r="E41">
-        <v>-25.24484084252747</v>
+        <v>-24.35748636072446</v>
       </c>
       <c r="F41">
-        <v>7.686951966834299</v>
+        <v>7.297967201827707</v>
       </c>
       <c r="G41">
-        <v>-3.130737719519546</v>
+        <v>-3.760780883280403</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.754418903105829</v>
       </c>
       <c r="E42">
-        <v>-24.77029299431567</v>
+        <v>-24.32966341642133</v>
       </c>
       <c r="F42">
-        <v>7.505279398256729</v>
+        <v>7.470121828947112</v>
       </c>
       <c r="G42">
-        <v>-3.656872790439297</v>
+        <v>-4.65332051339561</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.936729145699149</v>
       </c>
       <c r="E43">
-        <v>-24.77455428835689</v>
+        <v>-22.77419599342267</v>
       </c>
       <c r="F43">
-        <v>7.082995920392402</v>
+        <v>7.491140823425747</v>
       </c>
       <c r="G43">
-        <v>-3.916432802900316</v>
+        <v>-4.799338745496245</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.120856403328234</v>
       </c>
       <c r="E44">
-        <v>-23.21122090600691</v>
+        <v>-22.97815846272815</v>
       </c>
       <c r="F44">
-        <v>7.791523411028903</v>
+        <v>7.826463948078986</v>
       </c>
       <c r="G44">
-        <v>-3.91814104439858</v>
+        <v>-4.386725591663641</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.300618193852807</v>
       </c>
       <c r="E45">
-        <v>-22.77718931474174</v>
+        <v>-21.92162924894659</v>
       </c>
       <c r="F45">
-        <v>7.723231145607307</v>
+        <v>7.520145279667369</v>
       </c>
       <c r="G45">
-        <v>-4.789622294338484</v>
+        <v>-4.15030298197659</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.473989939903699</v>
       </c>
       <c r="E46">
-        <v>-22.71204721614141</v>
+        <v>-21.40090002280458</v>
       </c>
       <c r="F46">
-        <v>7.551805481802366</v>
+        <v>7.68785157383374</v>
       </c>
       <c r="G46">
-        <v>-5.011478503652743</v>
+        <v>-5.09093821768633</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.63762878825663</v>
       </c>
       <c r="E47">
-        <v>-22.68103622613688</v>
+        <v>-20.83704161021351</v>
       </c>
       <c r="F47">
-        <v>7.668761018668822</v>
+        <v>7.395282147573788</v>
       </c>
       <c r="G47">
-        <v>-4.924046995960591</v>
+        <v>-5.314045813214433</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.791976048394472</v>
       </c>
       <c r="E48">
-        <v>-21.29875123461355</v>
+        <v>-20.19850866123596</v>
       </c>
       <c r="F48">
-        <v>7.735384952141181</v>
+        <v>7.800194761001409</v>
       </c>
       <c r="G48">
-        <v>-5.067416791629808</v>
+        <v>-5.926536464526074</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.938273208980716</v>
       </c>
       <c r="E49">
-        <v>-20.96318225369717</v>
+        <v>-19.95555150225044</v>
       </c>
       <c r="F49">
-        <v>7.719276519626342</v>
+        <v>7.704751925585655</v>
       </c>
       <c r="G49">
-        <v>-5.772632512950896</v>
+        <v>-5.397249754252935</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.079995244975912</v>
       </c>
       <c r="E50">
-        <v>-20.45568522860556</v>
+        <v>-19.13154584334073</v>
       </c>
       <c r="F50">
-        <v>7.752507306357047</v>
+        <v>7.853641025830033</v>
       </c>
       <c r="G50">
-        <v>-5.29643371094551</v>
+        <v>-6.048215565821986</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.222450808830877</v>
       </c>
       <c r="E51">
-        <v>-20.23888000701434</v>
+        <v>-18.91958608893771</v>
       </c>
       <c r="F51">
-        <v>7.944193180099658</v>
+        <v>7.981671834871919</v>
       </c>
       <c r="G51">
-        <v>-5.598153520849147</v>
+        <v>-6.322699517574039</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.36824422957515</v>
       </c>
       <c r="E52">
-        <v>-19.23126284098963</v>
+        <v>-18.13484229967451</v>
       </c>
       <c r="F52">
-        <v>7.870481735128947</v>
+        <v>7.762972900124016</v>
       </c>
       <c r="G52">
-        <v>-6.403989963290843</v>
+        <v>-5.770765365266747</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.522250161191728</v>
       </c>
       <c r="E53">
-        <v>-18.66393561730869</v>
+        <v>-17.3989833873241</v>
       </c>
       <c r="F53">
-        <v>7.639705203648226</v>
+        <v>7.763156797687437</v>
       </c>
       <c r="G53">
-        <v>-6.173446882481537</v>
+        <v>-6.50039304939442</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.683230306366029</v>
       </c>
       <c r="E54">
-        <v>-17.36398281171882</v>
+        <v>-16.78020817044202</v>
       </c>
       <c r="F54">
-        <v>7.79235674863612</v>
+        <v>7.860238143825928</v>
       </c>
       <c r="G54">
-        <v>-6.980739964960512</v>
+        <v>-6.785391293779198</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.855649474034126</v>
       </c>
       <c r="E55">
-        <v>-18.28468950458832</v>
+        <v>-16.91798699212539</v>
       </c>
       <c r="F55">
-        <v>7.480683513332806</v>
+        <v>7.875203429324904</v>
       </c>
       <c r="G55">
-        <v>-7.618466904918017</v>
+        <v>-7.747852956229353</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.036246241472735</v>
       </c>
       <c r="E56">
-        <v>-16.12432210906708</v>
+        <v>-15.77452919129259</v>
       </c>
       <c r="F56">
-        <v>7.732981029938257</v>
+        <v>7.973305324103643</v>
       </c>
       <c r="G56">
-        <v>-6.914876661456712</v>
+        <v>-8.274898427172404</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.228931264575905</v>
       </c>
       <c r="E57">
-        <v>-16.76451700800544</v>
+        <v>-15.31178254634479</v>
       </c>
       <c r="F57">
-        <v>7.498947357829729</v>
+        <v>7.958545473720562</v>
       </c>
       <c r="G57">
-        <v>-7.662159484945319</v>
+        <v>-7.38956585469619</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.429646143772137</v>
       </c>
       <c r="E58">
-        <v>-16.22447384022071</v>
+        <v>-15.64743303979332</v>
       </c>
       <c r="F58">
-        <v>7.902441806263757</v>
+        <v>7.867602330036815</v>
       </c>
       <c r="G58">
-        <v>-7.448801446030369</v>
+        <v>-8.261629760651006</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.641780634864667</v>
       </c>
       <c r="E59">
-        <v>-16.18777961533656</v>
+        <v>-15.26539285861022</v>
       </c>
       <c r="F59">
-        <v>7.795375319451921</v>
+        <v>7.982929296589369</v>
       </c>
       <c r="G59">
-        <v>-8.349557850174048</v>
+        <v>-8.848705353857662</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.85938463773243</v>
       </c>
       <c r="E60">
-        <v>-15.54436949985275</v>
+        <v>-14.61204274267957</v>
       </c>
       <c r="F60">
-        <v>7.634622341264649</v>
+        <v>7.694132255481765</v>
       </c>
       <c r="G60">
-        <v>-8.173608975852863</v>
+        <v>-8.098158332467333</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.083039961469234</v>
       </c>
       <c r="E61">
-        <v>-15.98832750614273</v>
+        <v>-15.40093008565979</v>
       </c>
       <c r="F61">
-        <v>7.372417550521716</v>
+        <v>7.974359007440005</v>
       </c>
       <c r="G61">
-        <v>-8.349998152730771</v>
+        <v>-9.099075291901663</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.303939435240192</v>
       </c>
       <c r="E62">
-        <v>-15.25045342285891</v>
+        <v>-13.41028083899802</v>
       </c>
       <c r="F62">
-        <v>7.784821918740255</v>
+        <v>7.862449884791403</v>
       </c>
       <c r="G62">
-        <v>-9.105997642624279</v>
+        <v>-9.527774386509584</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.519776058868182</v>
       </c>
       <c r="E63">
-        <v>-15.34279353634932</v>
+        <v>-14.78309226289729</v>
       </c>
       <c r="F63">
-        <v>7.491122599342885</v>
+        <v>7.325164160396421</v>
       </c>
       <c r="G63">
-        <v>-9.295840876573784</v>
+        <v>-9.614742417826239</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.719713149220192</v>
       </c>
       <c r="E64">
-        <v>-14.18815946166559</v>
+        <v>-13.06656060486782</v>
       </c>
       <c r="F64">
-        <v>7.247862571101977</v>
+        <v>7.209356740750245</v>
       </c>
       <c r="G64">
-        <v>-8.8816022448814</v>
+        <v>-9.031487194171902</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.899041660098504</v>
       </c>
       <c r="E65">
-        <v>-13.71642832428657</v>
+        <v>-13.77057075952228</v>
       </c>
       <c r="F65">
-        <v>7.539593689550295</v>
+        <v>7.31160875621701</v>
       </c>
       <c r="G65">
-        <v>-9.723924209711402</v>
+        <v>-9.217907324033803</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.046271351976873</v>
       </c>
       <c r="E66">
-        <v>-14.60995511616203</v>
+        <v>-14.333043459067</v>
       </c>
       <c r="F66">
-        <v>7.521184052390479</v>
+        <v>7.673807432886677</v>
       </c>
       <c r="G66">
-        <v>-9.572185354918908</v>
+        <v>-9.280728236187013</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.156944185894933</v>
       </c>
       <c r="E67">
-        <v>-13.02666022038624</v>
+        <v>-13.92729218797973</v>
       </c>
       <c r="F67">
-        <v>7.317341058644383</v>
+        <v>7.20341071953295</v>
       </c>
       <c r="G67">
-        <v>-8.932687273097892</v>
+        <v>-8.738066921935218</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.223397190758995</v>
       </c>
       <c r="E68">
-        <v>-13.37630369851846</v>
+        <v>-12.70283357257174</v>
       </c>
       <c r="F68">
-        <v>7.318088246041707</v>
+        <v>7.562778036419848</v>
       </c>
       <c r="G68">
-        <v>-10.09855878511749</v>
+        <v>-9.178094703378527</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.246317966005611</v>
       </c>
       <c r="E69">
-        <v>-13.57618148426902</v>
+        <v>-12.72014140022905</v>
       </c>
       <c r="F69">
-        <v>7.210412080821411</v>
+        <v>7.314060723729296</v>
       </c>
       <c r="G69">
-        <v>-9.214868243228752</v>
+        <v>-8.797703089279649</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.224646331408152</v>
       </c>
       <c r="E70">
-        <v>-13.80792161313754</v>
+        <v>-14.32159547677561</v>
       </c>
       <c r="F70">
-        <v>7.321308938503792</v>
+        <v>6.94890311869683</v>
       </c>
       <c r="G70">
-        <v>-9.76826896720994</v>
+        <v>-9.6381744591532</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.163637463851622</v>
       </c>
       <c r="E71">
-        <v>-13.71667286188298</v>
+        <v>-12.57943718433673</v>
       </c>
       <c r="F71">
-        <v>6.800002421308813</v>
+        <v>6.786703811024269</v>
       </c>
       <c r="G71">
-        <v>-9.867337042472631</v>
+        <v>-9.090530773864804</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.064704562495656</v>
       </c>
       <c r="E72">
-        <v>-14.01455135363353</v>
+        <v>-13.19561305713841</v>
       </c>
       <c r="F72">
-        <v>7.164179239336365</v>
+        <v>6.679509755632402</v>
       </c>
       <c r="G72">
-        <v>-8.909996793971729</v>
+        <v>-9.156609262828656</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.93255726484422</v>
       </c>
       <c r="E73">
-        <v>-13.22472208805972</v>
+        <v>-13.47386514253972</v>
       </c>
       <c r="F73">
-        <v>7.167696487328652</v>
+        <v>7.003084973779139</v>
       </c>
       <c r="G73">
-        <v>-9.05861711486623</v>
+        <v>-8.873352365397535</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.767398276981194</v>
       </c>
       <c r="E74">
-        <v>-13.67437691465134</v>
+        <v>-13.20606024667411</v>
       </c>
       <c r="F74">
-        <v>7.157853825848588</v>
+        <v>6.607633972826295</v>
       </c>
       <c r="G74">
-        <v>-8.562859609814829</v>
+        <v>-8.513754287830821</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.572181340537979</v>
       </c>
       <c r="E75">
-        <v>-13.78173797642519</v>
+        <v>-12.74979384803128</v>
       </c>
       <c r="F75">
-        <v>6.893778581510134</v>
+        <v>6.777686203477394</v>
       </c>
       <c r="G75">
-        <v>-8.707884678253683</v>
+        <v>-8.938705844888288</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.347316487423159</v>
       </c>
       <c r="E76">
-        <v>-15.08696192575999</v>
+        <v>-13.33898001574725</v>
       </c>
       <c r="F76">
-        <v>6.994300965839853</v>
+        <v>6.582231258052045</v>
       </c>
       <c r="G76">
-        <v>-8.050456681791974</v>
+        <v>-8.52211672586302</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.095198823327799</v>
       </c>
       <c r="E77">
-        <v>-14.3869458851803</v>
+        <v>-13.6026187155258</v>
       </c>
       <c r="F77">
-        <v>6.750010448549863</v>
+        <v>6.51238331864799</v>
       </c>
       <c r="G77">
-        <v>-8.057729950341754</v>
+        <v>-7.344489466633473</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.817809072911475</v>
       </c>
       <c r="E78">
-        <v>-14.52363787310183</v>
+        <v>-12.86063730631703</v>
       </c>
       <c r="F78">
-        <v>6.790759497828375</v>
+        <v>6.427354718220233</v>
       </c>
       <c r="G78">
-        <v>-8.153596728067969</v>
+        <v>-7.31892874452476</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.517506489185569</v>
       </c>
       <c r="E79">
-        <v>-15.20210290587901</v>
+        <v>-13.8679963493233</v>
       </c>
       <c r="F79">
-        <v>6.945372616826098</v>
+        <v>6.643762388731992</v>
       </c>
       <c r="G79">
-        <v>-7.648996755881176</v>
+        <v>-7.522984150474358</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.198635105616702</v>
       </c>
       <c r="E80">
-        <v>-16.01767201771243</v>
+        <v>-14.4261488846647</v>
       </c>
       <c r="F80">
-        <v>6.95006614653036</v>
+        <v>6.586618291817271</v>
       </c>
       <c r="G80">
-        <v>-7.884810225189002</v>
+        <v>-6.904815913562866</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.864386304696319</v>
       </c>
       <c r="E81">
-        <v>-16.77380037972117</v>
+        <v>-14.93808381428382</v>
       </c>
       <c r="F81">
-        <v>7.03742411609479</v>
+        <v>6.614391794098333</v>
       </c>
       <c r="G81">
-        <v>-7.588804416886147</v>
+        <v>-6.171463865703513</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.521568937661513</v>
       </c>
       <c r="E82">
-        <v>-17.82192474574449</v>
+        <v>-16.55292405999704</v>
       </c>
       <c r="F82">
-        <v>6.908709075578192</v>
+        <v>6.085805584167551</v>
       </c>
       <c r="G82">
-        <v>-6.610697116217397</v>
+        <v>-6.47781512881659</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.173075977016288</v>
       </c>
       <c r="E83">
-        <v>-17.23558245970533</v>
+        <v>-17.01373704654357</v>
       </c>
       <c r="F83">
-        <v>6.740306952793469</v>
+        <v>6.441365724471184</v>
       </c>
       <c r="G83">
-        <v>-6.81976799865899</v>
+        <v>-6.210097932146808</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.826229669542796</v>
       </c>
       <c r="E84">
-        <v>-19.37798539883815</v>
+        <v>-17.7865709491666</v>
       </c>
       <c r="F84">
-        <v>7.004155224463556</v>
+        <v>6.426062465071865</v>
       </c>
       <c r="G84">
-        <v>-6.158334242094764</v>
+        <v>-5.879943846606371</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.481413000023154</v>
       </c>
       <c r="E85">
-        <v>-19.44219463179291</v>
+        <v>-17.9325100810118</v>
       </c>
       <c r="F85">
-        <v>6.845266072932583</v>
+        <v>6.616905060798427</v>
       </c>
       <c r="G85">
-        <v>-5.91165225178151</v>
+        <v>-4.937001160655758</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.144817164743474</v>
       </c>
       <c r="E86">
-        <v>-20.72420562336439</v>
+        <v>-19.85352951133163</v>
       </c>
       <c r="F86">
-        <v>6.669198238202354</v>
+        <v>6.396859200653572</v>
       </c>
       <c r="G86">
-        <v>-5.408465882539987</v>
+        <v>-5.194065021780166</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.815751614548469</v>
       </c>
       <c r="E87">
-        <v>-21.44624816151739</v>
+        <v>-20.92829036146807</v>
       </c>
       <c r="F87">
-        <v>6.813557825488224</v>
+        <v>6.207573935644273</v>
       </c>
       <c r="G87">
-        <v>-5.479516810903824</v>
+        <v>-5.701336604217151</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.501213580502907</v>
       </c>
       <c r="E88">
-        <v>-23.72794243265214</v>
+        <v>-21.94273193782233</v>
       </c>
       <c r="F88">
-        <v>6.348492484738914</v>
+        <v>6.647142127735414</v>
       </c>
       <c r="G88">
-        <v>-4.667151972658686</v>
+        <v>-4.678474038402993</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.19967223795063</v>
       </c>
       <c r="E89">
-        <v>-24.14478393658418</v>
+        <v>-24.40917436304801</v>
       </c>
       <c r="F89">
-        <v>6.513798170171972</v>
+        <v>6.260340939202602</v>
       </c>
       <c r="G89">
-        <v>-4.862295390016565</v>
+        <v>-4.829100549894293</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.917029647412325</v>
       </c>
       <c r="E90">
-        <v>-26.53322339702774</v>
+        <v>-25.72719125145447</v>
       </c>
       <c r="F90">
-        <v>6.282595857846213</v>
+        <v>5.850426643396878</v>
       </c>
       <c r="G90">
-        <v>-4.283469676293773</v>
+        <v>-4.103958654972332</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.651099725660173</v>
       </c>
       <c r="E91">
-        <v>-27.8716682316828</v>
+        <v>-25.97220886611349</v>
       </c>
       <c r="F91">
-        <v>6.324203095754027</v>
+        <v>6.021327122268444</v>
       </c>
       <c r="G91">
-        <v>-3.795624375081232</v>
+        <v>-4.750385708607042</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.40724753507389</v>
       </c>
       <c r="E92">
-        <v>-28.12993616128826</v>
+        <v>-27.49934162724615</v>
       </c>
       <c r="F92">
-        <v>6.031893776858555</v>
+        <v>6.440481028084994</v>
       </c>
       <c r="G92">
-        <v>-4.01806986150148</v>
+        <v>-3.897887126789318</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.182881051617982</v>
       </c>
       <c r="E93">
-        <v>-31.54051786813612</v>
+        <v>-29.69679948912722</v>
       </c>
       <c r="F93">
-        <v>5.769026292193382</v>
+        <v>5.971528987481749</v>
       </c>
       <c r="G93">
-        <v>-4.05209233800857</v>
+        <v>-3.783660063502305</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.982241540975471</v>
       </c>
       <c r="E94">
-        <v>-33.46097803191601</v>
+        <v>-30.96507335479643</v>
       </c>
       <c r="F94">
-        <v>5.537257376564108</v>
+        <v>5.46800917515968</v>
       </c>
       <c r="G94">
-        <v>-3.632431032722859</v>
+        <v>-3.360032724660547</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.802702098447618</v>
       </c>
       <c r="E95">
-        <v>-34.95550804443045</v>
+        <v>-33.84338501949374</v>
       </c>
       <c r="F95">
-        <v>5.269436254830194</v>
+        <v>4.902749483572159</v>
       </c>
       <c r="G95">
-        <v>-3.296526529580707</v>
+        <v>-3.653721151085911</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.649326110366724</v>
       </c>
       <c r="E96">
-        <v>-36.42214718553166</v>
+        <v>-36.12449058900749</v>
       </c>
       <c r="F96">
-        <v>4.979462932010616</v>
+        <v>4.979428140579699</v>
       </c>
       <c r="G96">
-        <v>-4.336484752559662</v>
+        <v>-4.068227936966978</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.518791838783982</v>
       </c>
       <c r="E97">
-        <v>-39.01356870065803</v>
+        <v>-38.47250436198457</v>
       </c>
       <c r="F97">
-        <v>4.698845190638256</v>
+        <v>4.216486851988104</v>
       </c>
       <c r="G97">
-        <v>-3.033212358478156</v>
+        <v>-2.361092160913163</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.420258375621931</v>
       </c>
       <c r="E98">
-        <v>-42.10115020619779</v>
+        <v>-40.5375768147254</v>
       </c>
       <c r="F98">
-        <v>3.938912532453628</v>
+        <v>4.089118736868457</v>
       </c>
       <c r="G98">
-        <v>-4.121223149959631</v>
+        <v>-3.428104162039041</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.34796201679101</v>
       </c>
       <c r="E99">
-        <v>-44.03940274435381</v>
+        <v>-42.68216474256691</v>
       </c>
       <c r="F99">
-        <v>3.657395184081827</v>
+        <v>4.013888066081011</v>
       </c>
       <c r="G99">
-        <v>-4.105858908111874</v>
+        <v>-3.231394856641086</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.321800913345285</v>
       </c>
       <c r="E100">
-        <v>-47.0011855061975</v>
+        <v>-45.70414677363156</v>
       </c>
       <c r="F100">
-        <v>3.298112360670014</v>
+        <v>3.29518159679891</v>
       </c>
       <c r="G100">
-        <v>-3.433950585461394</v>
+        <v>-3.260590557751919</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.32559478979532</v>
       </c>
       <c r="E101">
-        <v>-48.43959527245339</v>
+        <v>-48.19625206105871</v>
       </c>
       <c r="F101">
-        <v>3.079065511612936</v>
+        <v>2.69240845900821</v>
       </c>
       <c r="G101">
-        <v>-3.652350585232653</v>
+        <v>-3.590714848382502</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.406611845397912</v>
       </c>
       <c r="E102">
-        <v>-51.25387544680073</v>
+        <v>-50.40111171370531</v>
       </c>
       <c r="F102">
-        <v>2.497089365836921</v>
+        <v>2.499862739901494</v>
       </c>
       <c r="G102">
-        <v>-3.586401207544832</v>
+        <v>-3.299006128189621</v>
       </c>
     </row>
   </sheetData>
